--- a/data/Encuesta_10clientes.xlsx
+++ b/data/Encuesta_10clientes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanjose.astudillo\Github\KVA_Beta\KVA-Beta\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eduardo/Documents/Proyectos/Solar/KVA2/KVA-Beta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F75B511-F3E3-4E8C-84F4-D16DF33DB10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6763DF4D-A9A8-B94A-B96F-095E9EF47036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
@@ -262,7 +262,7 @@
     <t>Metropolitana</t>
   </si>
   <si>
-    <t>Los Lagos</t>
+    <t>Antofagasta</t>
   </si>
 </sst>
 </file>
@@ -272,7 +272,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -283,6 +283,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -296,6 +297,14 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -513,7 +522,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -559,6 +568,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -836,23 +846,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="18.85546875" customWidth="1"/>
+    <col min="1" max="2" width="18.83203125" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="37.5703125" customWidth="1"/>
-    <col min="5" max="5" width="25.42578125" customWidth="1"/>
-    <col min="6" max="6" width="35.140625" customWidth="1"/>
-    <col min="7" max="8" width="37.5703125" customWidth="1"/>
-    <col min="9" max="9" width="35.85546875" customWidth="1"/>
-    <col min="10" max="11" width="37.5703125" customWidth="1"/>
-    <col min="12" max="12" width="32.28515625" customWidth="1"/>
-    <col min="13" max="13" width="36.5703125" customWidth="1"/>
-    <col min="14" max="15" width="37.5703125" customWidth="1"/>
-    <col min="16" max="24" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="37.5" customWidth="1"/>
+    <col min="5" max="5" width="25.5" customWidth="1"/>
+    <col min="6" max="6" width="35.1640625" customWidth="1"/>
+    <col min="7" max="8" width="37.5" customWidth="1"/>
+    <col min="9" max="9" width="35.83203125" customWidth="1"/>
+    <col min="10" max="11" width="37.5" customWidth="1"/>
+    <col min="12" max="12" width="32.33203125" customWidth="1"/>
+    <col min="13" max="13" width="36.5" customWidth="1"/>
+    <col min="14" max="15" width="37.5" customWidth="1"/>
+    <col min="16" max="24" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -908,7 +918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="4">
         <v>45616.597722916667</v>
       </c>
@@ -960,7 +970,7 @@
       </c>
       <c r="R2" s="7"/>
     </row>
-    <row r="3" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>45618.593217002315</v>
       </c>
@@ -1007,7 +1017,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A4" s="4">
         <v>45623.644971168978</v>
       </c>
@@ -1054,7 +1064,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>45644.813182928236</v>
       </c>
@@ -1101,7 +1111,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>45645.771291620375</v>
       </c>
@@ -1151,7 +1161,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>45646.510344826384</v>
       </c>
@@ -1198,7 +1208,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>45796.690636203704</v>
       </c>
@@ -1245,7 +1255,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>45796.691899548612</v>
       </c>
@@ -1295,7 +1305,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
         <v>45796.692855462963</v>
       </c>
@@ -1342,7 +1352,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A11" s="11">
         <v>45798.682001886569</v>
       </c>
@@ -1389,7 +1399,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="11">
         <v>45788.598668981482</v>
       </c>
@@ -1439,7 +1449,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="15">
         <v>45788.598668981482</v>
       </c>
@@ -1489,7 +1499,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="15">
         <v>45788.598668981482</v>
       </c>
@@ -1532,7 +1542,7 @@
       <c r="P14" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="R14" t="s">
+      <c r="R14" s="17" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1563,15 +1573,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AA99E0A26634CB42BEA9C6EBCCC3F3D9" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d4d1693588441e58126eb6f6fdc1c4a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e14f83a-67ec-4bc9-9da1-ece74f6f9d53" xmlns:ns3="e8d2ff9b-5f5c-45a4-9648-827360dcfaf3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4c65bcf5125c345469d66aa2f67f60f0" ns2:_="" ns3:_="">
     <xsd:import namespace="2e14f83a-67ec-4bc9-9da1-ece74f6f9d53"/>
@@ -1790,6 +1791,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD1AD957-440B-446E-85D0-6B32EAC8C1AD}">
   <ds:schemaRefs>
@@ -1802,14 +1812,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{341542C5-0866-471C-A860-B8E41FA67324}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C89D7B0-85BB-4349-B1FB-35870CDE3235}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1826,4 +1828,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{341542C5-0866-471C-A860-B8E41FA67324}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>